--- a/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/5-Project/Versioning.xlsx
+++ b/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/5-Project/Versioning.xlsx
@@ -201,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -232,6 +232,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -597,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:I93"/>
+  <dimension ref="B2:I96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -864,551 +867,608 @@
     <row r="33">
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Method Double CoastalTax(Double amount)</t>
-        </is>
-      </c>
+          <t>Spreadsheet Double CoastalTax(Double amount)</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>return SalesTaxCoastal(amount);</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>= SalesTaxCoastal(amount)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>Test CoastalTax CoastalTaxTest</t>
         </is>
       </c>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="5" t="n"/>
-    </row>
-    <row r="37">
-      <c r="B37" s="11" t="inlineStr">
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="C37" s="11" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>_context_.usState</t>
         </is>
       </c>
-      <c r="D37" s="11" t="inlineStr">
+      <c r="D38" s="11" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" s="7" t="inlineStr">
+    <row r="39">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>US State</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>Tax</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="9" t="n">
+    <row r="40">
+      <c r="B40" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t>TX</t>
         </is>
       </c>
-      <c r="D39" s="12" t="n">
+      <c r="D40" s="12" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="41" ht="16.5" customHeight="1">
-      <c r="B41" s="2" t="inlineStr">
+    <row r="42" ht="16.5" customHeight="1">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>A datatype field marked ": context" sets the runtime context field of the same name when the object is passed to a rule; ": context.&lt;name&gt;" names the context field explicitly.</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="3" t="inlineStr">
+    <row r="44">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>Datatype TaxRequest</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n"/>
-    </row>
-    <row r="44">
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>UsStatesEnum</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>usState : context</t>
-        </is>
-      </c>
+      <c r="C44" s="5" t="n"/>
     </row>
     <row r="45">
       <c r="B45" s="9" t="inlineStr">
         <is>
+          <t>UsStatesEnum</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>usState : context</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="9" t="inlineStr">
+        <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
+      <c r="C46" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="3" t="inlineStr">
+    <row r="48">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>Datatype ShipmentTaxRequest</t>
         </is>
       </c>
-      <c r="C47" s="5" t="n"/>
-    </row>
-    <row r="48">
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>UsStatesEnum</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="inlineStr">
-        <is>
-          <t>destination : context.usState</t>
-        </is>
-      </c>
+      <c r="C48" s="5" t="n"/>
     </row>
     <row r="49">
       <c r="B49" s="9" t="inlineStr">
         <is>
+          <t>UsStatesEnum</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>destination : context.usState</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="9" t="inlineStr">
+        <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="C49" s="9" t="inlineStr">
+      <c r="C50" s="9" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>Method Double TaxOfRequest(TaxRequest request)</t>
-        </is>
-      </c>
-    </row>
     <row r="52">
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>return SalesTax(request.amount);</t>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Spreadsheet Double TaxOfRequest(TaxRequest request)</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="n"/>
+    </row>
+    <row r="53">
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>Method Double TaxOfShipment(ShipmentTaxRequest request)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>return SalesTax(request.amount);</t>
-        </is>
-      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>= SalesTax(request.amount)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Spreadsheet Double TaxOfShipment(ShipmentTaxRequest request)</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="n"/>
     </row>
     <row r="57">
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>= SalesTax(request.amount)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>Test TaxOfRequest TaxOfRequestTest</t>
         </is>
       </c>
-      <c r="C57" s="4" t="n"/>
-      <c r="D57" s="5" t="n"/>
-    </row>
-    <row r="58">
-      <c r="B58" s="11" t="inlineStr">
+      <c r="C60" s="4" t="n"/>
+      <c r="D60" s="5" t="n"/>
+    </row>
+    <row r="61">
+      <c r="B61" s="11" t="inlineStr">
         <is>
           <t>request.usState</t>
         </is>
       </c>
-      <c r="C58" s="11" t="inlineStr">
+      <c r="C61" s="11" t="inlineStr">
         <is>
           <t>request.amount</t>
         </is>
       </c>
-      <c r="D58" s="11" t="inlineStr">
+      <c r="D61" s="11" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" s="7" t="inlineStr">
+    <row r="62">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>US State</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>Tax</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" s="9" t="inlineStr">
+    <row r="63">
+      <c r="B63" s="9" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="C60" s="9" t="n">
+      <c r="C63" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="D60" s="12" t="n">
+      <c r="D63" s="12" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="61">
-      <c r="B61" s="9" t="inlineStr">
+    <row r="64">
+      <c r="B64" s="9" t="inlineStr">
         <is>
           <t>FL</t>
         </is>
       </c>
-      <c r="C61" s="9" t="n">
+      <c r="C64" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="D61" s="12" t="n">
+      <c r="D64" s="12" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="63" ht="43.5" customHeight="1">
-      <c r="B63" s="2" t="inlineStr">
+    <row r="66" ht="43.5" customHeight="1">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Versions can differ by several dimensions. A version that matches the context in more dimensions is more specific: for usState NY and lob Auto the version with both properties wins over the version with the state only. Versions with different single dimensions, one with only a state and one with only a lob, would be ambiguous for a context that matches both, and OpenL warns about them.</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" s="3" t="inlineStr">
+    <row r="68">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>SmartRules Double PermitFee()</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="B66" s="7" t="inlineStr">
+    <row r="69">
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t>Fee</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="B67" s="12" t="n">
+    <row r="70">
+      <c r="B70" s="12" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="69">
-      <c r="B69" s="3" t="inlineStr">
+    <row r="72">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>SmartRules Double PermitFee()</t>
         </is>
       </c>
-      <c r="C69" s="4" t="n"/>
-      <c r="D69" s="5" t="n"/>
-    </row>
-    <row r="70">
-      <c r="B70" s="6" t="inlineStr">
+      <c r="C72" s="4" t="n"/>
+      <c r="D72" s="5" t="n"/>
+    </row>
+    <row r="73">
+      <c r="B73" s="6" t="inlineStr">
         <is>
           <t>properties</t>
         </is>
       </c>
-      <c r="C70" s="6" t="inlineStr">
+      <c r="C73" s="6" t="inlineStr">
         <is>
           <t>state</t>
         </is>
       </c>
-      <c r="D70" s="6" t="inlineStr">
+      <c r="D73" s="6" t="inlineStr">
         <is>
           <t>NY</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="B71" s="7" t="inlineStr">
+    <row r="74">
+      <c r="B74" s="7" t="inlineStr">
         <is>
           <t>Fee</t>
         </is>
       </c>
-      <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="n"/>
-    </row>
-    <row r="72">
-      <c r="B72" s="12" t="n">
+      <c r="C74" s="7" t="n"/>
+      <c r="D74" s="7" t="n"/>
+    </row>
+    <row r="75">
+      <c r="B75" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="C72" s="9" t="n"/>
-      <c r="D72" s="9" t="n"/>
-    </row>
-    <row r="74">
-      <c r="B74" s="3" t="inlineStr">
+      <c r="C75" s="9" t="n"/>
+      <c r="D75" s="9" t="n"/>
+    </row>
+    <row r="77">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>SmartRules Double PermitFee()</t>
         </is>
       </c>
-      <c r="C74" s="4" t="n"/>
-      <c r="D74" s="5" t="n"/>
-    </row>
-    <row r="75">
-      <c r="B75" s="6" t="inlineStr">
+      <c r="C77" s="4" t="n"/>
+      <c r="D77" s="5" t="n"/>
+    </row>
+    <row r="78">
+      <c r="B78" s="6" t="inlineStr">
         <is>
           <t>properties</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
+      <c r="C78" s="6" t="inlineStr">
         <is>
           <t>state</t>
         </is>
       </c>
-      <c r="D75" s="6" t="inlineStr">
+      <c r="D78" s="6" t="inlineStr">
         <is>
           <t>NY</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="B76" s="10" t="n"/>
-      <c r="C76" s="6" t="inlineStr">
+    <row r="79">
+      <c r="B79" s="10" t="n"/>
+      <c r="C79" s="6" t="inlineStr">
         <is>
           <t>lob</t>
         </is>
       </c>
-      <c r="D76" s="6" t="inlineStr">
+      <c r="D79" s="6" t="inlineStr">
         <is>
           <t>Auto</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="B77" s="7" t="inlineStr">
+    <row r="80">
+      <c r="B80" s="7" t="inlineStr">
         <is>
           <t>Fee</t>
         </is>
       </c>
-      <c r="C77" s="7" t="n"/>
-      <c r="D77" s="7" t="n"/>
-    </row>
-    <row r="78">
-      <c r="B78" s="12" t="n">
+      <c r="C80" s="7" t="n"/>
+      <c r="D80" s="7" t="n"/>
+    </row>
+    <row r="81">
+      <c r="B81" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="C78" s="9" t="n"/>
-      <c r="D78" s="9" t="n"/>
-    </row>
-    <row r="80">
-      <c r="B80" s="3" t="inlineStr">
+      <c r="C81" s="9" t="n"/>
+      <c r="D81" s="9" t="n"/>
+    </row>
+    <row r="83">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>Test PermitFee PermitFeeTest</t>
         </is>
       </c>
-      <c r="C80" s="4" t="n"/>
-      <c r="D80" s="5" t="n"/>
-    </row>
-    <row r="81">
-      <c r="B81" s="11" t="inlineStr">
+      <c r="C83" s="4" t="n"/>
+      <c r="D83" s="5" t="n"/>
+    </row>
+    <row r="84">
+      <c r="B84" s="11" t="inlineStr">
         <is>
           <t>_context_.usState</t>
         </is>
       </c>
-      <c r="C81" s="11" t="inlineStr">
+      <c r="C84" s="11" t="inlineStr">
         <is>
           <t>_context_.lob</t>
         </is>
       </c>
-      <c r="D81" s="11" t="inlineStr">
+      <c r="D84" s="11" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="B82" s="7" t="inlineStr">
+    <row r="85">
+      <c r="B85" s="7" t="inlineStr">
         <is>
           <t>US State</t>
         </is>
       </c>
-      <c r="C82" s="7" t="inlineStr">
+      <c r="C85" s="7" t="inlineStr">
         <is>
           <t>Line Of Business</t>
         </is>
       </c>
-      <c r="D82" s="7" t="inlineStr">
+      <c r="D85" s="7" t="inlineStr">
         <is>
           <t>Fee</t>
         </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" s="9" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
-      <c r="C83" s="9" t="inlineStr">
-        <is>
-          <t>Auto</t>
-        </is>
-      </c>
-      <c r="D83" s="12" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
-      <c r="C84" s="9" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="D84" s="12" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="B85" s="9" t="inlineStr">
-        <is>
-          <t>TX</t>
-        </is>
-      </c>
-      <c r="C85" s="9" t="inlineStr">
-        <is>
-          <t>Auto</t>
-        </is>
-      </c>
-      <c r="D85" s="12" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="86">
       <c r="B86" s="9" t="inlineStr">
         <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="D86" s="12" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="9" t="inlineStr">
+        <is>
           <t>TX</t>
         </is>
       </c>
-      <c r="C86" s="9" t="inlineStr">
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="D88" s="12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="9" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="D86" s="12" t="n">
+      <c r="D89" s="12" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="88" ht="30" customHeight="1">
-      <c r="B88" s="2" t="inlineStr">
+    <row r="91" ht="30" customHeight="1">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>Module properties can also come from the file or folder names of the modules: a pattern such as ".*-%state%" in rules.xml sets the state of "Rates-CA.xlsx" to CA. It applies to every module of the project, so it is not used in this example.</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="B90" s="3" t="inlineStr">
+    <row r="93">
+      <c r="B93" s="3" t="inlineStr">
         <is>
           <t>Test TaxOfShipment TaxOfShipmentTest</t>
         </is>
       </c>
-      <c r="C90" s="4" t="n"/>
-      <c r="D90" s="5" t="n"/>
-    </row>
-    <row r="91">
-      <c r="B91" s="11" t="inlineStr">
+      <c r="C93" s="4" t="n"/>
+      <c r="D93" s="5" t="n"/>
+    </row>
+    <row r="94">
+      <c r="B94" s="11" t="inlineStr">
         <is>
           <t>request.destination</t>
         </is>
       </c>
-      <c r="C91" s="11" t="inlineStr">
+      <c r="C94" s="11" t="inlineStr">
         <is>
           <t>request.amount</t>
         </is>
       </c>
-      <c r="D91" s="11" t="inlineStr">
+      <c r="D94" s="11" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="B92" s="7" t="inlineStr">
+    <row r="95">
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="C92" s="7" t="inlineStr">
+      <c r="C95" s="7" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D92" s="7" t="inlineStr">
+      <c r="D95" s="7" t="inlineStr">
         <is>
           <t>Tax</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="B93" s="9" t="inlineStr">
+    <row r="96">
+      <c r="B96" s="9" t="inlineStr">
         <is>
           <t>TX</t>
         </is>
       </c>
-      <c r="C93" s="9" t="n">
+      <c r="C96" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="D93" s="12" t="n">
+      <c r="D96" s="12" t="n">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B57:D57"/>
+  <mergeCells count="23">
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B91:I91"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B66:I66"/>
     <mergeCell ref="B31:I31"/>
-    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="B56:C56"/>
     <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B52:C52"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="B42:I42"/>
+    <mergeCell ref="B83:D83"/>
     <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B88:I88"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B33:C33"/>
     <mergeCell ref="B6:I6"/>
-    <mergeCell ref="B63:I63"/>
-    <mergeCell ref="B41:I41"/>
+    <mergeCell ref="B93:D93"/>
+    <mergeCell ref="B77:D77"/>
     <mergeCell ref="B4:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
